--- a/data/trending_integrated_20261013_11.xlsx
+++ b/data/trending_integrated_20261013_11.xlsx
@@ -578,13 +578,13 @@
         <v>0.57</v>
       </c>
       <c r="E2" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G2" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H2" t="n">
         <v>1.84</v>
@@ -610,7 +610,7 @@
         <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>86867954970</v>
+        <v>86888991850</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>호남 반도체 관련 수혜 기대감 속 급등세 지속, 연이은 상한가 기록.</t>
+          <t>호남 반도체 클러스터 및 경제자유구역 확대 관련 수혜주로 부각. 연이은 급등 및 주도주로서의 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['호남반도체', '상한가', '대장주']</t>
+          <t>['호남 반도체', '수혜주', '주도주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19220</v>
+        <v>19060</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.55%</t>
+          <t>'+16.57%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.25</v>
       </c>
       <c r="E3" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F3" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G3" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="H3" t="n">
         <v>0.88</v>
@@ -702,7 +702,7 @@
         <v>1.13</v>
       </c>
       <c r="O3" t="n">
-        <v>197811467245</v>
+        <v>201995611130</v>
       </c>
       <c r="P3" t="n">
         <v>19930</v>
@@ -711,14 +711,14 @@
         <v>6320</v>
       </c>
       <c r="R3" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>보안 기술 중요성 부각 속 신고가 경신 기대, 전 세계적인 불황 가능성 언급.</t>
+          <t>미국 보안주 폭락 속에서 보안 기술의 중요성 부각. 라온시큐어의 신고가 돌파 및 상승 기대감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['보안', 'AI', '신고가']</t>
+          <t>['보안 기술', '신고가', '상승 기대']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12710</v>
+        <v>12580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.81%</t>
+          <t>'+13.64%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.92</v>
       </c>
       <c r="E4" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F4" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G4" t="n">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="H4" t="n">
         <v>15.64</v>
@@ -794,7 +794,7 @@
         <v>14.72</v>
       </c>
       <c r="O4" t="n">
-        <v>276227300905</v>
+        <v>278877429255</v>
       </c>
       <c r="P4" t="n">
         <v>14350</v>
@@ -803,23 +803,23 @@
         <v>465</v>
       </c>
       <c r="R4" t="n">
-        <v>-233000</v>
+        <v>-176000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>급등 기대감 속 투자자 이탈 관찰, 호남 클러스터 외 테마 소멸 전망.</t>
+          <t>호남 클러스터 테마 외 모든 테마 소멸 및 개인 매도 자제 권고. 주가 급등 기대감 존재.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['호남클러스터', '매도', '물갈이']</t>
+          <t>['호남 클러스터', '테마', '매도']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1668</v>
+        <v>18550</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.70%</t>
+          <t>'+3.46%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.42</v>
       </c>
       <c r="E5" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="F5" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="H5" t="n">
-        <v>0.32</v>
+        <v>0.46</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1578</v>
+        <v>17930</v>
       </c>
       <c r="K5" t="n">
-        <v>1578</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1776</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1457</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.26</v>
+        <v>0.88</v>
       </c>
       <c r="O5" t="n">
-        <v>7835192223</v>
+        <v>61731000000</v>
       </c>
       <c r="P5" t="n">
-        <v>2930</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>910</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>112000</v>
+        <v>-65000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>장성지역 경제자유구역 추가 편입에 따른 수혜 기대감. 광주 지역구를 넘어 전국구 성장 가능성 언급.</t>
+          <t>국내 해킹 초비상 및 프랑스 매장 AI 해킹 등 보안 이슈 부각. 다만, 뚜렷한 개별 뉴스는 부족하며 타 보안주 대비 상승세가 더딘 편.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['경제자유구역', '전국구', '수혜주']</t>
+          <t>['해킹', '보안주', 'AI']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,86 +924,86 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13580</v>
+        <v>1629</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.34%</t>
+          <t>'+3.23%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.01</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="F6" t="n">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>259</v>
+        <v>164</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>13400</v>
+        <v>1578</v>
       </c>
       <c r="K6" t="n">
-        <v>13750</v>
+        <v>1578</v>
       </c>
       <c r="L6" t="n">
-        <v>15390</v>
+        <v>1776</v>
       </c>
       <c r="M6" t="n">
-        <v>12380</v>
+        <v>1457</v>
       </c>
       <c r="N6" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="O6" t="n">
-        <v>160411142765</v>
+        <v>7975837888</v>
       </c>
       <c r="P6" t="n">
-        <v>19380</v>
+        <v>2930</v>
       </c>
       <c r="Q6" t="n">
-        <v>3200</v>
+        <v>910</v>
       </c>
       <c r="R6" t="n">
-        <v>-29000</v>
+        <v>34000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>호남 반도체 투자 기대감에 따른 주가 상승 지속 예상, 공매도 세력에 대한 경고.</t>
+          <t>장성지역 경제자유구역 추가 편입에 따른 수혜 기대감. 광주 지역구를 넘어 전국구 성장 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['호남반도체', '공매도', '상승예상']</t>
+          <t>['경제자유구역', '전국구', '수혜주']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,43 +1011,43 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6290</v>
+        <v>13520</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.29%</t>
+          <t>'+0.82%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.06</v>
+        <v>0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="F7" t="n">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="G7" t="n">
-        <v>86</v>
+        <v>177</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,183 +1055,183 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>6210</v>
+        <v>13410</v>
       </c>
       <c r="K7" t="n">
-        <v>5950</v>
+        <v>13260</v>
       </c>
       <c r="L7" t="n">
-        <v>6560</v>
+        <v>14580</v>
       </c>
       <c r="M7" t="n">
-        <v>5840</v>
+        <v>12920</v>
       </c>
       <c r="N7" t="n">
-        <v>0.75</v>
+        <v>0.21</v>
       </c>
       <c r="O7" t="n">
-        <v>18813810690</v>
+        <v>51193155035</v>
       </c>
       <c r="P7" t="n">
-        <v>11370</v>
+        <v>28700</v>
       </c>
       <c r="Q7" t="n">
-        <v>3300</v>
+        <v>11600</v>
       </c>
       <c r="R7" t="n">
-        <v>46000</v>
+        <v>34000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
+          <t>공매도 상환 및 공매도 수량 언급. 단기적 주가 상승 기대와 하락 경고.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['보안주', '시총', '신용매수']</t>
+          <t>['공매도', '상환', '주가']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18640</v>
+        <v>13490</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.49%</t>
+          <t>'+0.67%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.42</v>
+        <v>-1.01</v>
       </c>
       <c r="E8" t="n">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="F8" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="G8" t="n">
-        <v>77</v>
+        <v>255</v>
       </c>
       <c r="H8" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>18550</v>
+        <v>13400</v>
       </c>
       <c r="K8" t="n">
-        <v>17550</v>
+        <v>13750</v>
       </c>
       <c r="L8" t="n">
-        <v>19580</v>
+        <v>15390</v>
       </c>
       <c r="M8" t="n">
-        <v>17010</v>
+        <v>12380</v>
       </c>
       <c r="N8" t="n">
-        <v>0.88</v>
+        <v>1.01</v>
       </c>
       <c r="O8" t="n">
-        <v>60540181730</v>
+        <v>162060197695</v>
       </c>
       <c r="P8" t="n">
-        <v>30550</v>
+        <v>19380</v>
       </c>
       <c r="Q8" t="n">
-        <v>6100</v>
+        <v>3200</v>
       </c>
       <c r="R8" t="n">
-        <v>-5000</v>
+        <v>-76000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>국내 해킹 초비상 및 프랑스 매장 AI 해킹 등 보안 이슈 부각. 다만, 뚜렷한 개별 뉴스는 부족하며 타 보안주 대비 상승세가 더딘 편.</t>
+          <t>호남 반도체 투자 관련 언급과 함께 주가 상승 기대감 표출. 공매도 세력에 대한 경계.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['해킹', '보안주', 'AI']</t>
+          <t>['호남 반도체', '투자', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43400</v>
+        <v>6250</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.25%</t>
+          <t>'+0.64%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.23</v>
+        <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>146</v>
+        <v>54</v>
       </c>
       <c r="F9" t="n">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="G9" t="n">
-        <v>505</v>
+        <v>87</v>
       </c>
       <c r="H9" t="n">
-        <v>13.1</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,275 +1239,275 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>44400</v>
+        <v>6210</v>
       </c>
       <c r="K9" t="n">
-        <v>43300</v>
+        <v>5950</v>
       </c>
       <c r="L9" t="n">
-        <v>44100</v>
+        <v>6560</v>
       </c>
       <c r="M9" t="n">
-        <v>42250</v>
+        <v>5840</v>
       </c>
       <c r="N9" t="n">
-        <v>13.33</v>
+        <v>0.75</v>
       </c>
       <c r="O9" t="n">
-        <v>15845283950</v>
+        <v>19196595750</v>
       </c>
       <c r="P9" t="n">
-        <v>69200</v>
+        <v>11370</v>
       </c>
       <c r="Q9" t="n">
-        <v>24150</v>
+        <v>3300</v>
       </c>
       <c r="R9" t="n">
-        <v>32000</v>
+        <v>-5000</v>
       </c>
       <c r="S9" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>리보&amp;캄렐 간암 1차 승인 기대감 및 통합 IR 데이 예정. 공매도 세력에 대한 경계와 개미 투자자들의 매수세 언급.</t>
+          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['리보', '캄렐', '공매도']</t>
+          <t>['보안주', '시총', '신용매수']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17440</v>
+        <v>43700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.16%</t>
+          <t>'-1.58%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.08</v>
+        <v>-0.23</v>
       </c>
       <c r="E10" t="n">
-        <v>69</v>
+        <v>151</v>
       </c>
       <c r="F10" t="n">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="G10" t="n">
-        <v>245</v>
+        <v>516</v>
       </c>
       <c r="H10" t="n">
-        <v>27.69</v>
+        <v>13.1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>18010</v>
+        <v>44400</v>
       </c>
       <c r="K10" t="n">
-        <v>17430</v>
+        <v>43300</v>
       </c>
       <c r="L10" t="n">
-        <v>17840</v>
+        <v>44100</v>
       </c>
       <c r="M10" t="n">
-        <v>17290</v>
+        <v>42250</v>
       </c>
       <c r="N10" t="n">
-        <v>27.61</v>
+        <v>13.33</v>
       </c>
       <c r="O10" t="n">
-        <v>36314529550</v>
+        <v>16647126100</v>
       </c>
       <c r="P10" t="n">
-        <v>35350</v>
+        <v>69200</v>
       </c>
       <c r="Q10" t="n">
-        <v>17290</v>
+        <v>24150</v>
       </c>
       <c r="R10" t="n">
-        <v>520000</v>
+        <v>45000</v>
       </c>
       <c r="S10" t="n">
-        <v>25000</v>
+        <v>7000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>FLNG 매출 확대 전망 및 목표가 42,000원 제시. 주주 환원 정책 및 공매도 금지 촉구.</t>
+          <t>리보&amp;캄렐 간암 1차 승인 기대감 및 통합 IR 데이 예정. 공매도 세력에 대한 경계와 개미 투자자들의 매수세 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['FLNG', '매출확대', '주주환원']</t>
+          <t>['리보', '캄렐', '공매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12960</v>
+        <v>17460</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.36%</t>
+          <t>'-3.05%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E11" t="n">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="F11" t="n">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="G11" t="n">
-        <v>177</v>
+        <v>244</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3</v>
+        <v>27.69</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>13410</v>
+        <v>18010</v>
       </c>
       <c r="K11" t="n">
-        <v>13260</v>
+        <v>17430</v>
       </c>
       <c r="L11" t="n">
-        <v>14580</v>
+        <v>17840</v>
       </c>
       <c r="M11" t="n">
-        <v>12920</v>
+        <v>17290</v>
       </c>
       <c r="N11" t="n">
-        <v>0.21</v>
+        <v>27.61</v>
       </c>
       <c r="O11" t="n">
-        <v>49949067005</v>
+        <v>38060856970</v>
       </c>
       <c r="P11" t="n">
-        <v>28700</v>
+        <v>35350</v>
       </c>
       <c r="Q11" t="n">
-        <v>11600</v>
+        <v>17290</v>
       </c>
       <c r="R11" t="n">
-        <v>50000</v>
+        <v>681000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>71000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>주가 조작 및 장난질에 대한 경고, 종가 하락세 지속.</t>
+          <t>FLNG 매출 확대 전망 및 목표가 42,000원 제시. 주주 환원 정책 및 공매도 금지 촉구.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주가조작', '공매도', '종가하락']</t>
+          <t>['FLNG', '매출확대', '주주환원']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6550</v>
+        <v>15510</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.82%</t>
+          <t>'-3.60%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.3</v>
+        <v>0.16</v>
       </c>
       <c r="E12" t="n">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="F12" t="n">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="G12" t="n">
-        <v>503</v>
+        <v>205</v>
       </c>
       <c r="H12" t="n">
-        <v>12.27</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>6810</v>
+        <v>16090</v>
       </c>
       <c r="K12" t="n">
-        <v>7150</v>
+        <v>15190</v>
       </c>
       <c r="L12" t="n">
-        <v>7160</v>
+        <v>15980</v>
       </c>
       <c r="M12" t="n">
-        <v>6440</v>
+        <v>15100</v>
       </c>
       <c r="N12" t="n">
-        <v>12.57</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>17193543640</v>
+        <v>37274200725</v>
       </c>
       <c r="P12" t="n">
-        <v>8850</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>4220</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>-595000</v>
+        <v>395000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>31000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>영업이익 호조에도 불구하고 의도적 주가 누르기 의혹 제기, 광주 조감도 관련 언급.</t>
+          <t>금감원 사모펀드 점검 및 유사 국가 국장 상황에 대한 우려. 주가 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['영업이익', '광주', '주가조작']</t>
+          <t>['금감원', '사모펀드', '주가 하락']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15460</v>
+        <v>6540</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.92%</t>
+          <t>'-3.96%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.16</v>
+        <v>-0.3</v>
       </c>
       <c r="E13" t="n">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="F13" t="n">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="G13" t="n">
-        <v>198</v>
+        <v>524</v>
       </c>
       <c r="H13" t="n">
-        <v>9.630000000000001</v>
+        <v>12.27</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>16090</v>
+        <v>6810</v>
       </c>
       <c r="K13" t="n">
-        <v>15190</v>
+        <v>7150</v>
       </c>
       <c r="L13" t="n">
-        <v>15980</v>
+        <v>7160</v>
       </c>
       <c r="M13" t="n">
-        <v>15100</v>
+        <v>6440</v>
       </c>
       <c r="N13" t="n">
-        <v>9.470000000000001</v>
+        <v>12.57</v>
       </c>
       <c r="O13" t="n">
-        <v>36056986200</v>
+        <v>17447642450</v>
       </c>
       <c r="P13" t="n">
-        <v>40350</v>
+        <v>8850</v>
       </c>
       <c r="Q13" t="n">
-        <v>3320</v>
+        <v>4220</v>
       </c>
       <c r="R13" t="n">
-        <v>300000</v>
+        <v>-606000</v>
       </c>
       <c r="S13" t="n">
-        <v>-2000</v>
+        <v>-8000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>증시 전반의 불안정성 속 주가 하락 우려, 도배성 게시글에 대한 불만.</t>
+          <t>의도적인 주가 누르기 및 공매도에 대한 불만 제기. 호남 테마 및 중국 테마 관련 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['증시', '하락', '뱅크런']</t>
+          <t>['공매도', '호남 테마', '중국 테마']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
@@ -1682,13 +1682,13 @@
         <v>-0.11</v>
       </c>
       <c r="E14" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F14" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G14" t="n">
-        <v>607</v>
+        <v>624</v>
       </c>
       <c r="H14" t="n">
         <v>22.1</v>
@@ -1714,7 +1714,7 @@
         <v>22.21</v>
       </c>
       <c r="O14" t="n">
-        <v>89800512400</v>
+        <v>91796462150</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1723,14 +1723,14 @@
         <v>57000</v>
       </c>
       <c r="R14" t="n">
-        <v>211000</v>
+        <v>225000</v>
       </c>
       <c r="S14" t="n">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정부 정책 및 특정 정치인 관련 부정적 언급, 주가 하락 및 개미 물량 소화 언급.</t>
+          <t>정부 정책 및 정치인 관련 부정적 언급. 주가 하락 및 반대매매 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['정부정책', '주가하락', '개미물량']</t>
+          <t>['반대매매', '주가', '신용']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7080</v>
+        <v>7100</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.45%</t>
+          <t>'-4.18%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.19</v>
       </c>
       <c r="E15" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F15" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G15" t="n">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="H15" t="n">
         <v>1.8</v>
@@ -1806,7 +1806,7 @@
         <v>1.99</v>
       </c>
       <c r="O15" t="n">
-        <v>58850198085</v>
+        <v>59326353625</v>
       </c>
       <c r="P15" t="n">
         <v>23500</v>
@@ -1815,23 +1815,23 @@
         <v>2890</v>
       </c>
       <c r="R15" t="n">
-        <v>-19000</v>
+        <v>-241000</v>
       </c>
       <c r="S15" t="n">
-        <v>-5000</v>
+        <v>-130000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>수도권 거점 공장 기반 건설기초소재 대장주로서의 입지, 성수 메가프로젝트 수혜 기대감. 다만, 프로그램 매매에 따른 변동성 우려.</t>
+          <t>호남 반도체 클러스터 및 신도시 개발 관련 언급. 대차 물량 증가 및 매집 흔적 포착.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['건설기초소재', '수도권', '메가프로젝트']</t>
+          <t>['호남 반도체', '신도시 개발', '매집']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7400</v>
+        <v>7390</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.64%</t>
+          <t>'-4.77%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.36</v>
       </c>
       <c r="E16" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G16" t="n">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="H16" t="n">
         <v>26.01</v>
@@ -1898,7 +1898,7 @@
         <v>26.37</v>
       </c>
       <c r="O16" t="n">
-        <v>13734017620</v>
+        <v>14319311545</v>
       </c>
       <c r="P16" t="n">
         <v>17950</v>
@@ -1907,10 +1907,10 @@
         <v>7370</v>
       </c>
       <c r="R16" t="n">
-        <v>-406000</v>
+        <v>-510000</v>
       </c>
       <c r="S16" t="n">
-        <v>31000</v>
+        <v>19000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>174500</v>
+        <v>174600</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.58%</t>
+          <t>'-6.53%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>41</v>
       </c>
       <c r="F17" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G17" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H17" t="n">
         <v>75.20999999999999</v>
@@ -1990,7 +1990,7 @@
         <v>75.23</v>
       </c>
       <c r="O17" t="n">
-        <v>368913314700</v>
+        <v>383919588400</v>
       </c>
       <c r="P17" t="n">
         <v>243500</v>
@@ -1999,10 +1999,10 @@
         <v>70400</v>
       </c>
       <c r="R17" t="n">
-        <v>-134000</v>
+        <v>-173000</v>
       </c>
       <c r="S17" t="n">
-        <v>3000</v>
+        <v>65000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>231500</v>
+        <v>233500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-7.58%</t>
+          <t>'-6.79%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2053,10 +2053,10 @@
         <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="G18" t="n">
-        <v>1770</v>
+        <v>1987</v>
       </c>
       <c r="H18" t="n">
         <v>46.3</v>
@@ -2082,7 +2082,7 @@
         <v>46.35</v>
       </c>
       <c r="O18" t="n">
-        <v>2344401474250</v>
+        <v>2462806673750</v>
       </c>
       <c r="P18" t="n">
         <v>374500</v>
@@ -2091,23 +2091,23 @@
         <v>90200</v>
       </c>
       <c r="R18" t="n">
-        <v>-1776000</v>
+        <v>-2204000</v>
       </c>
       <c r="S18" t="n">
-        <v>217000</v>
+        <v>241000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>정치적 이슈로 인한 주가 폭락 우려, 정부 정책 비판.</t>
+          <t>정치적 이슈와 정부 정책에 대한 강한 부정적 인식 표출. 주가 하락 원인으로 지목.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['이재명', '정치', '경제']</t>
+          <t>['정부 정책', '주가 하락', '탄핵']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14490</v>
+        <v>14540</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-7.82%</t>
+          <t>'-7.51%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F19" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G19" t="n">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="H19" t="n">
         <v>3.43</v>
@@ -2174,7 +2174,7 @@
         <v>3.37</v>
       </c>
       <c r="O19" t="n">
-        <v>55690000715</v>
+        <v>57055418575</v>
       </c>
       <c r="P19" t="n">
         <v>31500</v>
@@ -2183,14 +2183,14 @@
         <v>1272</v>
       </c>
       <c r="R19" t="n">
-        <v>201000</v>
+        <v>85000</v>
       </c>
       <c r="S19" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>3분기 어닝 서프라이즈에도 불구하고 주가 하락, 미국 AI 거품론 및 광케이블 기술력 우려.</t>
+          <t>3분기 어닝 서프라이즈 달성 및 외인 대량 매수에도 불구하고 주가 하락. 미국 AI 거품론 및 광케이블 기술력 이슈.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['어닝서프라이즈', '광케이블', 'AI']</t>
+          <t>['어닝 서프라이즈', '외인 매수', 'AI 거품론']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1461000</v>
+        <v>1479000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-8.97%</t>
+          <t>'-7.85%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2237,10 +2237,10 @@
         <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="G20" t="n">
-        <v>2030</v>
+        <v>2116</v>
       </c>
       <c r="H20" t="n">
         <v>49.41</v>
@@ -2266,7 +2266,7 @@
         <v>49.52</v>
       </c>
       <c r="O20" t="n">
-        <v>3265829706500</v>
+        <v>3401819442500</v>
       </c>
       <c r="P20" t="n">
         <v>2987000</v>
@@ -2275,23 +2275,23 @@
         <v>403000</v>
       </c>
       <c r="R20" t="n">
-        <v>-636000</v>
+        <v>-722000</v>
       </c>
       <c r="S20" t="n">
-        <v>46000</v>
+        <v>88000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>호남 반도체 이슈로 인한 외국인 자금 이탈 및 주가 급락에 대한 우려, 정치권 비판.</t>
+          <t>호남 반도체 및 특정 정치인 관련 이슈로 인한 외국인 자금 이탈 우려. 주가 급락에 대한 불만.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['호남반도체', '외국인', '주가급락']</t>
+          <t>['호남 반도체', '외국인 자금', '주가 급락']</t>
         </is>
       </c>
       <c r="X20" t="n">

--- a/data/trending_integrated_20261013_11.xlsx
+++ b/data/trending_integrated_20261013_11.xlsx
@@ -578,13 +578,13 @@
         <v>0.57</v>
       </c>
       <c r="E2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F2" t="n">
         <v>65</v>
       </c>
       <c r="G2" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H2" t="n">
         <v>1.84</v>
@@ -610,7 +610,7 @@
         <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>86888991850</v>
+        <v>86910678450</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -655,83 +655,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19060</v>
+        <v>12630</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.57%</t>
+          <t>'+14.09%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.25</v>
+        <v>0.92</v>
       </c>
       <c r="E3" t="n">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="F3" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G3" t="n">
-        <v>131</v>
+        <v>272</v>
       </c>
       <c r="H3" t="n">
-        <v>0.88</v>
+        <v>15.64</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>16350</v>
+        <v>11070</v>
       </c>
       <c r="K3" t="n">
-        <v>15790</v>
+        <v>11670</v>
       </c>
       <c r="L3" t="n">
-        <v>19930</v>
+        <v>13970</v>
       </c>
       <c r="M3" t="n">
-        <v>15520</v>
+        <v>11200</v>
       </c>
       <c r="N3" t="n">
-        <v>1.13</v>
+        <v>14.72</v>
       </c>
       <c r="O3" t="n">
-        <v>201995611130</v>
+        <v>281974532815</v>
       </c>
       <c r="P3" t="n">
-        <v>19930</v>
+        <v>14350</v>
       </c>
       <c r="Q3" t="n">
-        <v>6320</v>
+        <v>465</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-176000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 보안주 폭락 속에서 보안 기술의 중요성 부각. 라온시큐어의 신고가 돌파 및 상승 기대감.</t>
+          <t>호남 클러스터 외 테마 소멸 및 물갈이 통한 상승 기대감. 일부 매도 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['보안 기술', '신고가', '상승 기대']</t>
+          <t>['호남 클러스터', '물갈이', '매도']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,90 +740,90 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12580</v>
+        <v>18620</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.64%</t>
+          <t>'+13.88%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.92</v>
+        <v>-0.25</v>
       </c>
       <c r="E4" t="n">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="F4" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G4" t="n">
-        <v>272</v>
+        <v>130</v>
       </c>
       <c r="H4" t="n">
-        <v>15.64</v>
+        <v>0.88</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>11070</v>
+        <v>16350</v>
       </c>
       <c r="K4" t="n">
-        <v>11670</v>
+        <v>15790</v>
       </c>
       <c r="L4" t="n">
-        <v>13970</v>
+        <v>19930</v>
       </c>
       <c r="M4" t="n">
-        <v>11200</v>
+        <v>15520</v>
       </c>
       <c r="N4" t="n">
-        <v>14.72</v>
+        <v>1.13</v>
       </c>
       <c r="O4" t="n">
-        <v>278877429255</v>
+        <v>205801564260</v>
       </c>
       <c r="P4" t="n">
-        <v>14350</v>
+        <v>19930</v>
       </c>
       <c r="Q4" t="n">
-        <v>465</v>
+        <v>6320</v>
       </c>
       <c r="R4" t="n">
-        <v>-176000</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>호남 클러스터 테마 외 모든 테마 소멸 및 개인 매도 자제 권고. 주가 급등 기대감 존재.</t>
+          <t>보안 기술 중요성 부각 및 신고가 돌파 기대감. AI 해킹 관련 뉴스 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['호남 클러스터', '테마', '매도']</t>
+          <t>['보안 기술', 'AI 해킹', '신고가']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18550</v>
+        <v>1628</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.46%</t>
+          <t>'+3.17%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.42</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="G5" t="n">
-        <v>80</v>
+        <v>168</v>
       </c>
       <c r="H5" t="n">
-        <v>0.46</v>
+        <v>0.32</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>17930</v>
+        <v>1578</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1578</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1776</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1457</v>
       </c>
       <c r="N5" t="n">
-        <v>0.88</v>
+        <v>1.26</v>
       </c>
       <c r="O5" t="n">
-        <v>61731000000</v>
+        <v>8088859317</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2930</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>910</v>
       </c>
       <c r="R5" t="n">
-        <v>-65000</v>
+        <v>34000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>국내 해킹 초비상 및 프랑스 매장 AI 해킹 등 보안 이슈 부각. 다만, 뚜렷한 개별 뉴스는 부족하며 타 보안주 대비 상승세가 더딘 편.</t>
+          <t>장성지역 경제자유구역 추가 편입에 따른 수혜 기대감. 광주 지역구를 넘어 전국구 성장 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['해킹', '보안주', 'AI']</t>
+          <t>['경제자유구역', '전국구', '수혜주']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1629</v>
+        <v>13710</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.23%</t>
+          <t>'+2.24%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="E6" t="n">
-        <v>62</v>
+        <v>125</v>
       </c>
       <c r="F6" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="G6" t="n">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="H6" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,28 +963,28 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1578</v>
+        <v>13410</v>
       </c>
       <c r="K6" t="n">
-        <v>1578</v>
+        <v>13260</v>
       </c>
       <c r="L6" t="n">
-        <v>1776</v>
+        <v>14580</v>
       </c>
       <c r="M6" t="n">
-        <v>1457</v>
+        <v>12920</v>
       </c>
       <c r="N6" t="n">
-        <v>1.26</v>
+        <v>0.21</v>
       </c>
       <c r="O6" t="n">
-        <v>7975837888</v>
+        <v>54368677025</v>
       </c>
       <c r="P6" t="n">
-        <v>2930</v>
+        <v>28700</v>
       </c>
       <c r="Q6" t="n">
-        <v>910</v>
+        <v>11600</v>
       </c>
       <c r="R6" t="n">
         <v>34000</v>
@@ -994,112 +994,112 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>장성지역 경제자유구역 추가 편입에 따른 수혜 기대감. 광주 지역구를 넘어 전국구 성장 가능성 언급.</t>
+          <t>공매도 및 대차 관련 의혹 제기, 주가 하락 및 상승에 대한 상반된 전망 혼재.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['경제자유구역', '전국구', '수혜주']</t>
+          <t>['공매도', '대차', '주가']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13520</v>
+        <v>13460</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.82%</t>
+          <t>'+0.45%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.09</v>
+        <v>-1.01</v>
       </c>
       <c r="E7" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F7" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G7" t="n">
-        <v>177</v>
+        <v>258</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>13410</v>
+        <v>13400</v>
       </c>
       <c r="K7" t="n">
-        <v>13260</v>
+        <v>13750</v>
       </c>
       <c r="L7" t="n">
-        <v>14580</v>
+        <v>15390</v>
       </c>
       <c r="M7" t="n">
-        <v>12920</v>
+        <v>12380</v>
       </c>
       <c r="N7" t="n">
-        <v>0.21</v>
+        <v>1.01</v>
       </c>
       <c r="O7" t="n">
-        <v>51193155035</v>
+        <v>163213343750</v>
       </c>
       <c r="P7" t="n">
-        <v>28700</v>
+        <v>19380</v>
       </c>
       <c r="Q7" t="n">
-        <v>11600</v>
+        <v>3200</v>
       </c>
       <c r="R7" t="n">
-        <v>34000</v>
+        <v>-76000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>공매도 상환 및 공매도 수량 언급. 단기적 주가 상승 기대와 하락 경고.</t>
+          <t>서산 대비 금호건설의 상대적 부진 및 상승 기대. 호남 반도체 투자 뉴스 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['공매도', '상환', '주가']</t>
+          <t>['호남 반도체', '속도전', '투자']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,130 +1108,130 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13490</v>
+        <v>6080</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.67%</t>
+          <t>'-2.09%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.01</v>
+        <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>114</v>
+        <v>57</v>
       </c>
       <c r="F8" t="n">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="G8" t="n">
-        <v>255</v>
+        <v>90</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>13400</v>
+        <v>6210</v>
       </c>
       <c r="K8" t="n">
-        <v>13750</v>
+        <v>5950</v>
       </c>
       <c r="L8" t="n">
-        <v>15390</v>
+        <v>6560</v>
       </c>
       <c r="M8" t="n">
-        <v>12380</v>
+        <v>5840</v>
       </c>
       <c r="N8" t="n">
-        <v>1.01</v>
+        <v>0.75</v>
       </c>
       <c r="O8" t="n">
-        <v>162060197695</v>
+        <v>19856231130</v>
       </c>
       <c r="P8" t="n">
-        <v>19380</v>
+        <v>11370</v>
       </c>
       <c r="Q8" t="n">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="R8" t="n">
-        <v>-76000</v>
+        <v>-5000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>호남 반도체 투자 관련 언급과 함께 주가 상승 기대감 표출. 공매도 세력에 대한 경계.</t>
+          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['호남 반도체', '투자', '공매도']</t>
+          <t>['보안주', '시총', '신용매수']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6250</v>
+        <v>43400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.64%</t>
+          <t>'-2.25%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.06</v>
+        <v>-0.23</v>
       </c>
       <c r="E9" t="n">
-        <v>54</v>
+        <v>154</v>
       </c>
       <c r="F9" t="n">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="G9" t="n">
-        <v>87</v>
+        <v>533</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6899999999999999</v>
+        <v>13.1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,91 +1239,91 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>6210</v>
+        <v>44400</v>
       </c>
       <c r="K9" t="n">
-        <v>5950</v>
+        <v>43300</v>
       </c>
       <c r="L9" t="n">
-        <v>6560</v>
+        <v>44100</v>
       </c>
       <c r="M9" t="n">
-        <v>5840</v>
+        <v>42250</v>
       </c>
       <c r="N9" t="n">
-        <v>0.75</v>
+        <v>13.33</v>
       </c>
       <c r="O9" t="n">
-        <v>19196595750</v>
+        <v>17057315475</v>
       </c>
       <c r="P9" t="n">
-        <v>11370</v>
+        <v>69200</v>
       </c>
       <c r="Q9" t="n">
-        <v>3300</v>
+        <v>24150</v>
       </c>
       <c r="R9" t="n">
-        <v>-5000</v>
+        <v>45000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
+          <t>간암 1차 치료제 승인 기대감 속 공매도 우려 및 악성 매물대 소화 필요성 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['보안주', '시총', '신용매수']</t>
+          <t>['캄렐리주맙', '공매도', '승인']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>43700</v>
+        <v>18090</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.58%</t>
+          <t>'-2.48%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.23</v>
+        <v>-0.42</v>
       </c>
       <c r="E10" t="n">
-        <v>151</v>
+        <v>79</v>
       </c>
       <c r="F10" t="n">
-        <v>95</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
-        <v>516</v>
+        <v>82</v>
       </c>
       <c r="H10" t="n">
-        <v>13.1</v>
+        <v>0.46</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,60 +1331,60 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>44400</v>
+        <v>18550</v>
       </c>
       <c r="K10" t="n">
-        <v>43300</v>
+        <v>17550</v>
       </c>
       <c r="L10" t="n">
-        <v>44100</v>
+        <v>19580</v>
       </c>
       <c r="M10" t="n">
-        <v>42250</v>
+        <v>17010</v>
       </c>
       <c r="N10" t="n">
-        <v>13.33</v>
+        <v>0.88</v>
       </c>
       <c r="O10" t="n">
-        <v>16647126100</v>
+        <v>63657341175</v>
       </c>
       <c r="P10" t="n">
-        <v>69200</v>
+        <v>30550</v>
       </c>
       <c r="Q10" t="n">
-        <v>24150</v>
+        <v>6100</v>
       </c>
       <c r="R10" t="n">
-        <v>45000</v>
+        <v>-65000</v>
       </c>
       <c r="S10" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>리보&amp;캄렐 간암 1차 승인 기대감 및 통합 IR 데이 예정. 공매도 세력에 대한 경계와 개미 투자자들의 매수세 언급.</t>
+          <t>국내 해킹 초비상 및 프랑스 매장 AI 해킹 등 보안 이슈 부각. 다만, 뚜렷한 개별 뉴스는 부족하며 타 보안주 대비 상승세가 더딘 편.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['리보', '캄렐', '공매도']</t>
+          <t>['해킹', '보안주', 'AI']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17460</v>
+        <v>17450</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.05%</t>
+          <t>'-3.11%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.08</v>
       </c>
       <c r="E11" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F11" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G11" t="n">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="H11" t="n">
         <v>27.69</v>
@@ -1438,7 +1438,7 @@
         <v>27.61</v>
       </c>
       <c r="O11" t="n">
-        <v>38060856970</v>
+        <v>39397924950</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15510</v>
+        <v>15480</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.60%</t>
+          <t>'-3.79%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.16</v>
       </c>
       <c r="E12" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G12" t="n">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="H12" t="n">
         <v>9.630000000000001</v>
@@ -1530,7 +1530,7 @@
         <v>9.470000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>37274200725</v>
+        <v>39021760310</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>금감원 사모펀드 점검 및 유사 국가 국장 상황에 대한 우려. 주가 하락 가능성 언급.</t>
+          <t>국장 전반의 하락세 속 대우건설의 부진에 대한 우려. 도배성 게시글에 대한 불만.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['금감원', '사모펀드', '주가 하락']</t>
+          <t>['국장', '하락세', '건설주']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6540</v>
+        <v>6530</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.96%</t>
+          <t>'-4.11%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.3</v>
       </c>
       <c r="E13" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F13" t="n">
         <v>77</v>
       </c>
       <c r="G13" t="n">
-        <v>524</v>
+        <v>539</v>
       </c>
       <c r="H13" t="n">
         <v>12.27</v>
@@ -1622,7 +1622,7 @@
         <v>12.57</v>
       </c>
       <c r="O13" t="n">
-        <v>17447642450</v>
+        <v>17611718690</v>
       </c>
       <c r="P13" t="n">
         <v>8850</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>의도적인 주가 누르기 및 공매도에 대한 불만 제기. 호남 테마 및 중국 테마 관련 언급.</t>
+          <t>의도적 주가 누르기 및 공매도 의혹 제기. 호남 테마 및 부지 관련 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공매도', '호남 테마', '중국 테마']</t>
+          <t>['공매도', '호남 테마', '주가 조작']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>68600</v>
+        <v>68500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.06%</t>
+          <t>'-4.20%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.11</v>
       </c>
       <c r="E14" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F14" t="n">
         <v>130</v>
       </c>
       <c r="G14" t="n">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="H14" t="n">
         <v>22.1</v>
@@ -1714,7 +1714,7 @@
         <v>22.21</v>
       </c>
       <c r="O14" t="n">
-        <v>91796462150</v>
+        <v>95252839700</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7100</v>
+        <v>7070</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.18%</t>
+          <t>'-4.59%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.19</v>
       </c>
       <c r="E15" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F15" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G15" t="n">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="H15" t="n">
         <v>1.8</v>
@@ -1806,7 +1806,7 @@
         <v>1.99</v>
       </c>
       <c r="O15" t="n">
-        <v>59326353625</v>
+        <v>59714075995</v>
       </c>
       <c r="P15" t="n">
         <v>23500</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>호남 반도체 클러스터 및 신도시 개발 관련 언급. 대차 물량 증가 및 매집 흔적 포착.</t>
+          <t>성수 메가프로젝트 및 건설 기초 소재 관련 긍정적 언급과 함께 매집 흔적 발견. 일부 매도.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['호남 반도체', '신도시 개발', '매집']</t>
+          <t>['성수 메가프로젝트', '건설 기초 소재', '매집']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1866,13 +1866,13 @@
         <v>-0.36</v>
       </c>
       <c r="E16" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F16" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G16" t="n">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="H16" t="n">
         <v>26.01</v>
@@ -1898,7 +1898,7 @@
         <v>26.37</v>
       </c>
       <c r="O16" t="n">
-        <v>14319311545</v>
+        <v>14930658125</v>
       </c>
       <c r="P16" t="n">
         <v>17950</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>지속적인 저점 갱신 및 회사 문제 가능성 제기. 아이폰 주문 감축 영향 우려, 기관 매수 관찰.</t>
+          <t>지속적인 저점 갱신 및 아이폰 패널 출하량 감소 우려. 회사 문제 가능성 제기.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['저점갱신', '아이폰주문', '기관매수']</t>
+          <t>['아이폰', '패널', '저점 갱신']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>174600</v>
+        <v>173700</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.53%</t>
+          <t>'-7.01%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.02</v>
       </c>
       <c r="E17" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F17" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G17" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="H17" t="n">
         <v>75.20999999999999</v>
@@ -1984,13 +1984,13 @@
         <v>183000</v>
       </c>
       <c r="M17" t="n">
-        <v>173800</v>
+        <v>173600</v>
       </c>
       <c r="N17" t="n">
         <v>75.23</v>
       </c>
       <c r="O17" t="n">
-        <v>383919588400</v>
+        <v>402270514800</v>
       </c>
       <c r="P17" t="n">
         <v>243500</v>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>233500</v>
+        <v>232000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-6.79%</t>
+          <t>'-7.39%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2053,10 +2053,10 @@
         <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="G18" t="n">
-        <v>1987</v>
+        <v>1970</v>
       </c>
       <c r="H18" t="n">
         <v>46.3</v>
@@ -2082,7 +2082,7 @@
         <v>46.35</v>
       </c>
       <c r="O18" t="n">
-        <v>2462806673750</v>
+        <v>2606417665250</v>
       </c>
       <c r="P18" t="n">
         <v>374500</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>정치적 이슈와 정부 정책에 대한 강한 부정적 인식 표출. 주가 하락 원인으로 지목.</t>
+          <t>현 정권 및 특정 정치인에 대한 강한 부정적 인식으로 인한 증시 하락 우려.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['정부 정책', '주가 하락', '탄핵']</t>
+          <t>['정권', '증시', '하락']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14540</v>
+        <v>14420</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-7.51%</t>
+          <t>'-8.27%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F19" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G19" t="n">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="H19" t="n">
         <v>3.43</v>
@@ -2174,7 +2174,7 @@
         <v>3.37</v>
       </c>
       <c r="O19" t="n">
-        <v>57055418575</v>
+        <v>58757899195</v>
       </c>
       <c r="P19" t="n">
         <v>31500</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>3분기 어닝 서프라이즈 달성 및 외인 대량 매수에도 불구하고 주가 하락. 미국 AI 거품론 및 광케이블 기술력 이슈.</t>
+          <t>3분기 어닝 서프라이즈 달성 및 외인 대량 매수 확인. 광케이블 기술력 관련 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['어닝 서프라이즈', '외인 매수', 'AI 거품론']</t>
+          <t>['어닝 서프라이즈', '외인 매수', '광케이블']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1479000</v>
+        <v>1470000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-7.85%</t>
+          <t>'-8.41%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2237,10 +2237,10 @@
         <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="G20" t="n">
-        <v>2116</v>
+        <v>2135</v>
       </c>
       <c r="H20" t="n">
         <v>49.41</v>
@@ -2266,7 +2266,7 @@
         <v>49.52</v>
       </c>
       <c r="O20" t="n">
-        <v>3401819442500</v>
+        <v>3524545315000</v>
       </c>
       <c r="P20" t="n">
         <v>2987000</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>호남 반도체 및 특정 정치인 관련 이슈로 인한 외국인 자금 이탈 우려. 주가 급락에 대한 불만.</t>
+          <t>호남 반도체 사업 및 특정 정치인 관련 악재로 인한 주가 하락 우려. 외국인 이탈 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['호남 반도체', '외국인 자금', '주가 급락']</t>
+          <t>['호남 반도체', '정치인', '외국인']</t>
         </is>
       </c>
       <c r="X20" t="n">

--- a/data/trending_integrated_20261013_11.xlsx
+++ b/data/trending_integrated_20261013_11.xlsx
@@ -578,13 +578,13 @@
         <v>0.57</v>
       </c>
       <c r="E2" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="H2" t="n">
         <v>1.84</v>
@@ -610,7 +610,7 @@
         <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>86910678450</v>
+        <v>86978776130</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>호남 반도체 클러스터 및 경제자유구역 확대 관련 수혜주로 부각. 연이은 급등 및 주도주로서의 가능성 언급.</t>
+          <t>무차입 경영, 호남 반도체 관련 지역 경제자유구역 확대 수혜 기대감으로 인한 급등 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['호남 반도체', '수혜주', '주도주']</t>
+          <t>['경제자유구역', '수혜주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,83 +655,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12630</v>
+        <v>18600</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.09%</t>
+          <t>'+13.76%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.92</v>
+        <v>-0.25</v>
       </c>
       <c r="E3" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="F3" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G3" t="n">
-        <v>272</v>
+        <v>127</v>
       </c>
       <c r="H3" t="n">
-        <v>15.64</v>
+        <v>0.88</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>11070</v>
+        <v>16350</v>
       </c>
       <c r="K3" t="n">
-        <v>11670</v>
+        <v>15790</v>
       </c>
       <c r="L3" t="n">
-        <v>13970</v>
+        <v>19930</v>
       </c>
       <c r="M3" t="n">
-        <v>11200</v>
+        <v>15520</v>
       </c>
       <c r="N3" t="n">
-        <v>14.72</v>
+        <v>1.13</v>
       </c>
       <c r="O3" t="n">
-        <v>281974532815</v>
+        <v>210533413100</v>
       </c>
       <c r="P3" t="n">
-        <v>14350</v>
+        <v>19930</v>
       </c>
       <c r="Q3" t="n">
-        <v>465</v>
+        <v>6320</v>
       </c>
       <c r="R3" t="n">
-        <v>-176000</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>호남 클러스터 외 테마 소멸 및 물갈이 통한 상승 기대감. 일부 매도 언급.</t>
+          <t>미국 보안주 폭락 속 라온시큐어의 기술적 상승 가능성 및 AI 해킹 관련 이슈.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['호남 클러스터', '물갈이', '매도']</t>
+          <t>['보안', 'AI', '해킹']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,90 +740,90 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18620</v>
+        <v>12420</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.88%</t>
+          <t>'+12.20%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.25</v>
+        <v>0.92</v>
       </c>
       <c r="E4" t="n">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="F4" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G4" t="n">
-        <v>130</v>
+        <v>270</v>
       </c>
       <c r="H4" t="n">
-        <v>0.88</v>
+        <v>15.64</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>16350</v>
+        <v>11070</v>
       </c>
       <c r="K4" t="n">
-        <v>15790</v>
+        <v>11670</v>
       </c>
       <c r="L4" t="n">
-        <v>19930</v>
+        <v>13970</v>
       </c>
       <c r="M4" t="n">
-        <v>15520</v>
+        <v>11200</v>
       </c>
       <c r="N4" t="n">
-        <v>1.13</v>
+        <v>14.72</v>
       </c>
       <c r="O4" t="n">
-        <v>205801564260</v>
+        <v>286837144570</v>
       </c>
       <c r="P4" t="n">
-        <v>19930</v>
+        <v>14350</v>
       </c>
       <c r="Q4" t="n">
-        <v>6320</v>
+        <v>465</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-176000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>보안 기술 중요성 부각 및 신고가 돌파 기대감. AI 해킹 관련 뉴스 언급.</t>
+          <t>급등 기대감 속 투자자 이탈 관찰, 호남 클러스터 외 테마 소멸 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['보안 기술', 'AI 해킹', '신고가']</t>
+          <t>['호남클러스터', '매도', '물갈이']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
@@ -843,18 +843,18 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.17%</t>
+          <t>'+3.30%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.9399999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F5" t="n">
         <v>20</v>
@@ -886,7 +886,7 @@
         <v>1.26</v>
       </c>
       <c r="O5" t="n">
-        <v>8088859317</v>
+        <v>8167113049</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13710</v>
+        <v>13630</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.24%</t>
+          <t>'+1.64%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.09</v>
       </c>
       <c r="E6" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F6" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G6" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="H6" t="n">
         <v>0.3</v>
@@ -978,7 +978,7 @@
         <v>0.21</v>
       </c>
       <c r="O6" t="n">
-        <v>54368677025</v>
+        <v>55758296195</v>
       </c>
       <c r="P6" t="n">
         <v>28700</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>공매도 및 대차 관련 의혹 제기, 주가 하락 및 상승에 대한 상반된 전망 혼재.</t>
+          <t>주가 조작 및 매도세에 대한 의구심, 장 후반 하락 마감에 대한 실망감.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['공매도', '대차', '주가']</t>
+          <t>['공매도', '매도세']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13460</v>
+        <v>13190</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.45%</t>
+          <t>'-1.57%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-1.01</v>
       </c>
       <c r="E7" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="F7" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G7" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>1.01</v>
       </c>
       <c r="O7" t="n">
-        <v>163213343750</v>
+        <v>165985015500</v>
       </c>
       <c r="P7" t="n">
         <v>19380</v>
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6080</v>
+        <v>43250</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.09%</t>
+          <t>'-2.59%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.06</v>
+        <v>-0.23</v>
       </c>
       <c r="E8" t="n">
-        <v>57</v>
+        <v>167</v>
       </c>
       <c r="F8" t="n">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="G8" t="n">
-        <v>90</v>
+        <v>554</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6899999999999999</v>
+        <v>13.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,91 +1147,91 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>6210</v>
+        <v>44400</v>
       </c>
       <c r="K8" t="n">
-        <v>5950</v>
+        <v>43300</v>
       </c>
       <c r="L8" t="n">
-        <v>6560</v>
+        <v>44100</v>
       </c>
       <c r="M8" t="n">
-        <v>5840</v>
+        <v>42250</v>
       </c>
       <c r="N8" t="n">
-        <v>0.75</v>
+        <v>13.33</v>
       </c>
       <c r="O8" t="n">
-        <v>19856231130</v>
+        <v>18933185700</v>
       </c>
       <c r="P8" t="n">
-        <v>11370</v>
+        <v>69200</v>
       </c>
       <c r="Q8" t="n">
-        <v>3300</v>
+        <v>24150</v>
       </c>
       <c r="R8" t="n">
-        <v>-5000</v>
+        <v>45000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
+          <t>간암 1차 치료제 승인 기대감 속 공매도 우려 및 악성 매물대 소화 필요성 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['보안주', '시총', '신용매수']</t>
+          <t>['캄렐리주맙', '공매도', '승인']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43400</v>
+        <v>6045</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.25%</t>
+          <t>'-2.66%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.23</v>
+        <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>154</v>
+        <v>59</v>
       </c>
       <c r="F9" t="n">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="G9" t="n">
-        <v>533</v>
+        <v>99</v>
       </c>
       <c r="H9" t="n">
-        <v>13.1</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,60 +1239,60 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>44400</v>
+        <v>6210</v>
       </c>
       <c r="K9" t="n">
-        <v>43300</v>
+        <v>5950</v>
       </c>
       <c r="L9" t="n">
-        <v>44100</v>
+        <v>6560</v>
       </c>
       <c r="M9" t="n">
-        <v>42250</v>
+        <v>5840</v>
       </c>
       <c r="N9" t="n">
-        <v>13.33</v>
+        <v>0.75</v>
       </c>
       <c r="O9" t="n">
-        <v>17057315475</v>
+        <v>20230019295</v>
       </c>
       <c r="P9" t="n">
-        <v>69200</v>
+        <v>11370</v>
       </c>
       <c r="Q9" t="n">
-        <v>24150</v>
+        <v>3300</v>
       </c>
       <c r="R9" t="n">
-        <v>45000</v>
+        <v>-5000</v>
       </c>
       <c r="S9" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>간암 1차 치료제 승인 기대감 속 공매도 우려 및 악성 매물대 소화 필요성 언급.</t>
+          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['캄렐리주맙', '공매도', '승인']</t>
+          <t>['보안주', '시총', '신용매수']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18090</v>
+        <v>17950</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.48%</t>
+          <t>'-3.23%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.42</v>
       </c>
       <c r="E10" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G10" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H10" t="n">
         <v>0.46</v>
@@ -1346,7 +1346,7 @@
         <v>0.88</v>
       </c>
       <c r="O10" t="n">
-        <v>63657341175</v>
+        <v>65426657480</v>
       </c>
       <c r="P10" t="n">
         <v>30550</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>국내 해킹 초비상 및 프랑스 매장 AI 해킹 등 보안 이슈 부각. 다만, 뚜렷한 개별 뉴스는 부족하며 타 보안주 대비 상승세가 더딘 편.</t>
+          <t>국내 해킹 초비상 상황 속 보안주 급등 기대감, 아이온큐 주가와의 연관성 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['해킹', '보안주', 'AI']</t>
+          <t>['해킹', '보안주']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17450</v>
+        <v>17360</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.11%</t>
+          <t>'-3.61%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1412,7 +1412,7 @@
         <v>48</v>
       </c>
       <c r="G11" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H11" t="n">
         <v>27.69</v>
@@ -1438,7 +1438,7 @@
         <v>27.61</v>
       </c>
       <c r="O11" t="n">
-        <v>39397924950</v>
+        <v>41677922725</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15480</v>
+        <v>15390</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.79%</t>
+          <t>'-4.35%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.16</v>
       </c>
       <c r="E12" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G12" t="n">
-        <v>222</v>
+        <v>251</v>
       </c>
       <c r="H12" t="n">
         <v>9.630000000000001</v>
@@ -1530,7 +1530,7 @@
         <v>9.470000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>39021760310</v>
+        <v>40243372730</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>국장 전반의 하락세 속 대우건설의 부진에 대한 우려. 도배성 게시글에 대한 불만.</t>
+          <t>전반적인 시장 하락 속에서 대우건설 주가 하락에 대한 우려와 도배 글에 대한 불만.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['국장', '하락세', '건설주']</t>
+          <t>['공매도', '시장']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6530</v>
+        <v>6510</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.11%</t>
+          <t>'-4.41%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.3</v>
       </c>
       <c r="E13" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F13" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G13" t="n">
-        <v>539</v>
+        <v>553</v>
       </c>
       <c r="H13" t="n">
         <v>12.27</v>
@@ -1622,7 +1622,7 @@
         <v>12.57</v>
       </c>
       <c r="O13" t="n">
-        <v>17611718690</v>
+        <v>17788246410</v>
       </c>
       <c r="P13" t="n">
         <v>8850</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>의도적 주가 누르기 및 공매도 의혹 제기. 호남 테마 및 부지 관련 언급.</t>
+          <t>의도적인 주가 누르기와 공매도에 대한 불만, 광주 송정역 부지 관련 기대감.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공매도', '호남 테마', '주가 조작']</t>
+          <t>['공매도', '부지']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>68500</v>
+        <v>68100</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.20%</t>
+          <t>'-4.76%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.11</v>
       </c>
       <c r="E14" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F14" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G14" t="n">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="H14" t="n">
         <v>22.1</v>
@@ -1714,7 +1714,7 @@
         <v>22.21</v>
       </c>
       <c r="O14" t="n">
-        <v>95252839700</v>
+        <v>100965186050</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정부 정책 및 정치인 관련 부정적 언급. 주가 하락 및 반대매매 우려.</t>
+          <t>정치적 요인 및 시장 상황으로 인한 주가 하락에 대한 불만, 정부 정책 비판.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['반대매매', '주가', '신용']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7070</v>
+        <v>7010</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.59%</t>
+          <t>'-5.40%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.19</v>
       </c>
       <c r="E15" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F15" t="n">
         <v>48</v>
       </c>
       <c r="G15" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H15" t="n">
         <v>1.8</v>
@@ -1806,7 +1806,7 @@
         <v>1.99</v>
       </c>
       <c r="O15" t="n">
-        <v>59714075995</v>
+        <v>60795787530</v>
       </c>
       <c r="P15" t="n">
         <v>23500</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>성수 메가프로젝트 및 건설 기초 소재 관련 긍정적 언급과 함께 매집 흔적 발견. 일부 매도.</t>
+          <t>호남 반도체 클러스터 및 신도시 개발 관련 언급. 대차 물량 증가 및 매집 흔적 포착.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['성수 메가프로젝트', '건설 기초 소재', '매집']</t>
+          <t>['호남 반도체', '신도시 개발', '매집']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7390</v>
+        <v>7335</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.77%</t>
+          <t>'-5.48%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.36</v>
       </c>
       <c r="E16" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F16" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G16" t="n">
-        <v>296</v>
+        <v>316</v>
       </c>
       <c r="H16" t="n">
         <v>26.01</v>
@@ -1892,19 +1892,19 @@
         <v>7680</v>
       </c>
       <c r="M16" t="n">
-        <v>7370</v>
+        <v>7330</v>
       </c>
       <c r="N16" t="n">
         <v>26.37</v>
       </c>
       <c r="O16" t="n">
-        <v>14930658125</v>
+        <v>16447368080</v>
       </c>
       <c r="P16" t="n">
         <v>17950</v>
       </c>
       <c r="Q16" t="n">
-        <v>7370</v>
+        <v>7330</v>
       </c>
       <c r="R16" t="n">
         <v>-510000</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>지속적인 저점 갱신 및 아이폰 패널 출하량 감소 우려. 회사 문제 가능성 제기.</t>
+          <t>아이폰 패널 출하량 감소 및 지속적인 주가 하락에 대한 우려, OLED 시장 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['아이폰', '패널', '저점 갱신']</t>
+          <t>['아이폰', 'OLED']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>173700</v>
+        <v>172500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-7.01%</t>
+          <t>'-7.66%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.02</v>
       </c>
       <c r="E17" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F17" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G17" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H17" t="n">
         <v>75.20999999999999</v>
@@ -1984,13 +1984,13 @@
         <v>183000</v>
       </c>
       <c r="M17" t="n">
-        <v>173600</v>
+        <v>172500</v>
       </c>
       <c r="N17" t="n">
         <v>75.23</v>
       </c>
       <c r="O17" t="n">
-        <v>402270514800</v>
+        <v>420087699300</v>
       </c>
       <c r="P17" t="n">
         <v>243500</v>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>232000</v>
+        <v>230500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-7.39%</t>
+          <t>'-7.98%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2053,10 +2053,10 @@
         <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>584</v>
+        <v>594</v>
       </c>
       <c r="G18" t="n">
-        <v>1970</v>
+        <v>2042</v>
       </c>
       <c r="H18" t="n">
         <v>46.3</v>
@@ -2082,7 +2082,7 @@
         <v>46.35</v>
       </c>
       <c r="O18" t="n">
-        <v>2606417665250</v>
+        <v>2736709972000</v>
       </c>
       <c r="P18" t="n">
         <v>374500</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>현 정권 및 특정 정치인에 대한 강한 부정적 인식으로 인한 증시 하락 우려.</t>
+          <t>정치적 이슈로 인한 국가 경제 부도 및 주가 하락에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['정권', '증시', '하락']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14420</v>
+        <v>14370</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-8.27%</t>
+          <t>'-8.59%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,7 +2145,7 @@
         <v>96</v>
       </c>
       <c r="F19" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G19" t="n">
         <v>326</v>
@@ -2168,13 +2168,13 @@
         <v>15130</v>
       </c>
       <c r="M19" t="n">
-        <v>14380</v>
+        <v>14360</v>
       </c>
       <c r="N19" t="n">
         <v>3.37</v>
       </c>
       <c r="O19" t="n">
-        <v>58757899195</v>
+        <v>60368443675</v>
       </c>
       <c r="P19" t="n">
         <v>31500</v>
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1470000</v>
+        <v>1462000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-8.41%</t>
+          <t>'-8.91%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2237,10 +2237,10 @@
         <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G20" t="n">
-        <v>2135</v>
+        <v>2102</v>
       </c>
       <c r="H20" t="n">
         <v>49.41</v>
@@ -2266,7 +2266,7 @@
         <v>49.52</v>
       </c>
       <c r="O20" t="n">
-        <v>3524545315000</v>
+        <v>3632607448500</v>
       </c>
       <c r="P20" t="n">
         <v>2987000</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>호남 반도체 사업 및 특정 정치인 관련 악재로 인한 주가 하락 우려. 외국인 이탈 언급.</t>
+          <t>호남 반도체 이슈 및 정치적 요인으로 인한 외국인 자금 유출 및 주가 하락에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['호남 반도체', '정치인', '외국인']</t>
+          <t>['호남 반도체', '외국인']</t>
         </is>
       </c>
       <c r="X20" t="n">

--- a/data/trending_integrated_20261013_11.xlsx
+++ b/data/trending_integrated_20261013_11.xlsx
@@ -578,13 +578,13 @@
         <v>0.57</v>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F2" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G2" t="n">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="H2" t="n">
         <v>1.84</v>
@@ -610,7 +610,7 @@
         <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>86978776130</v>
+        <v>87085119490</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -659,18 +659,18 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18600</v>
+        <v>18715</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+13.76%</t>
+          <t>'+14.46%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.25</v>
       </c>
       <c r="E3" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F3" t="n">
         <v>78</v>
@@ -702,7 +702,7 @@
         <v>1.13</v>
       </c>
       <c r="O3" t="n">
-        <v>210533413100</v>
+        <v>212840574715</v>
       </c>
       <c r="P3" t="n">
         <v>19930</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 보안주 폭락 속 라온시큐어의 기술적 상승 가능성 및 AI 해킹 관련 이슈.</t>
+          <t>보안 기술 중요성 부각 및 AI 관련 보안 이슈 언급. 신고가 돌파 기대감 속 급등 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['보안', 'AI', '해킹']</t>
+          <t>['보안 기술', 'AI', '신고가']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12420</v>
+        <v>12210</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+12.20%</t>
+          <t>'+10.30%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.92</v>
       </c>
       <c r="E4" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F4" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G4" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H4" t="n">
         <v>15.64</v>
@@ -794,7 +794,7 @@
         <v>14.72</v>
       </c>
       <c r="O4" t="n">
-        <v>286837144570</v>
+        <v>290435601395</v>
       </c>
       <c r="P4" t="n">
         <v>14350</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>급등 기대감 속 투자자 이탈 관찰, 호남 클러스터 외 테마 소멸 전망.</t>
+          <t>급등 기대감 속 개인 매물 소화 및 물량 확보 중. 호남클러스터 외 테마 소멸. 주포의 매집 정황 포착.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['호남클러스터', '매도', '물갈이']</t>
+          <t>['호남클러스터', '주포', '매집']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.30%</t>
+          <t>'+3.42%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.9399999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G5" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="H5" t="n">
         <v>0.32</v>
@@ -886,7 +886,7 @@
         <v>1.26</v>
       </c>
       <c r="O5" t="n">
-        <v>8167113049</v>
+        <v>8211539254</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13630</v>
+        <v>13500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.64%</t>
+          <t>'+0.67%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.09</v>
       </c>
       <c r="E6" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F6" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G6" t="n">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="H6" t="n">
         <v>0.3</v>
@@ -978,7 +978,7 @@
         <v>0.21</v>
       </c>
       <c r="O6" t="n">
-        <v>55758296195</v>
+        <v>56491641090</v>
       </c>
       <c r="P6" t="n">
         <v>28700</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>주가 조작 및 매도세에 대한 의구심, 장 후반 하락 마감에 대한 실망감.</t>
+          <t>주가 상승 시 매도세에 눌리는 현상 반복. 공매도 및 대차 상환 관련 언급. 종가 하락에 대한 우려.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['공매도', '매도세']</t>
+          <t>['공매도', '매도세', '주가']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,70 +1023,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13190</v>
+        <v>43300</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.57%</t>
+          <t>'-2.48%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.01</v>
+        <v>-0.23</v>
       </c>
       <c r="E7" t="n">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="F7" t="n">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="G7" t="n">
-        <v>259</v>
+        <v>573</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>13.1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>13400</v>
+        <v>44400</v>
       </c>
       <c r="K7" t="n">
-        <v>13750</v>
+        <v>43300</v>
       </c>
       <c r="L7" t="n">
-        <v>15390</v>
+        <v>44100</v>
       </c>
       <c r="M7" t="n">
-        <v>12380</v>
+        <v>42250</v>
       </c>
       <c r="N7" t="n">
-        <v>1.01</v>
+        <v>13.33</v>
       </c>
       <c r="O7" t="n">
-        <v>165985015500</v>
+        <v>19898568375</v>
       </c>
       <c r="P7" t="n">
-        <v>19380</v>
+        <v>69200</v>
       </c>
       <c r="Q7" t="n">
-        <v>3200</v>
+        <v>24150</v>
       </c>
       <c r="R7" t="n">
-        <v>-76000</v>
+        <v>45000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>서산 대비 금호건설의 상대적 부진 및 상승 기대. 호남 반도체 투자 뉴스 언급.</t>
+          <t>간암 1차 치료제 승인 기대감 속 공매도 우려 및 악성 매물대 소화 필요성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['호남 반도체', '속도전', '투자']</t>
+          <t>['캄렐리주맙', '공매도', '승인']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>43250</v>
+        <v>6010</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.59%</t>
+          <t>'-3.22%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.23</v>
+        <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>167</v>
+        <v>60</v>
       </c>
       <c r="F8" t="n">
-        <v>102</v>
+        <v>22</v>
       </c>
       <c r="G8" t="n">
-        <v>554</v>
+        <v>107</v>
       </c>
       <c r="H8" t="n">
-        <v>13.1</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,91 +1147,91 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>44400</v>
+        <v>6210</v>
       </c>
       <c r="K8" t="n">
-        <v>43300</v>
+        <v>5950</v>
       </c>
       <c r="L8" t="n">
-        <v>44100</v>
+        <v>6560</v>
       </c>
       <c r="M8" t="n">
-        <v>42250</v>
+        <v>5840</v>
       </c>
       <c r="N8" t="n">
-        <v>13.33</v>
+        <v>0.75</v>
       </c>
       <c r="O8" t="n">
-        <v>18933185700</v>
+        <v>20816244600</v>
       </c>
       <c r="P8" t="n">
-        <v>69200</v>
+        <v>11370</v>
       </c>
       <c r="Q8" t="n">
-        <v>24150</v>
+        <v>3300</v>
       </c>
       <c r="R8" t="n">
-        <v>45000</v>
+        <v>-5000</v>
       </c>
       <c r="S8" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>간암 1차 치료제 승인 기대감 속 공매도 우려 및 악성 매물대 소화 필요성 언급.</t>
+          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['캄렐리주맙', '공매도', '승인']</t>
+          <t>['보안주', '시총', '신용매수']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6045</v>
+        <v>17920</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.66%</t>
+          <t>'-3.40%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.06</v>
+        <v>-0.42</v>
       </c>
       <c r="E9" t="n">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="F9" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G9" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.46</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>6210</v>
+        <v>18550</v>
       </c>
       <c r="K9" t="n">
-        <v>5950</v>
+        <v>17550</v>
       </c>
       <c r="L9" t="n">
-        <v>6560</v>
+        <v>19580</v>
       </c>
       <c r="M9" t="n">
-        <v>5840</v>
+        <v>17010</v>
       </c>
       <c r="N9" t="n">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="O9" t="n">
-        <v>20230019295</v>
+        <v>66329191965</v>
       </c>
       <c r="P9" t="n">
-        <v>11370</v>
+        <v>30550</v>
       </c>
       <c r="Q9" t="n">
-        <v>3300</v>
+        <v>6100</v>
       </c>
       <c r="R9" t="n">
-        <v>-5000</v>
+        <v>-65000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
+          <t>국내 해킹 초비상 상황 속 보안주 급등 기대감, 아이온큐 주가와의 연관성 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['보안주', '시총', '신용매수']</t>
+          <t>['해킹', '보안주']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17950</v>
+        <v>12930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.23%</t>
+          <t>'-3.51%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.42</v>
+        <v>-1.01</v>
       </c>
       <c r="E10" t="n">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="F10" t="n">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="G10" t="n">
-        <v>85</v>
+        <v>263</v>
       </c>
       <c r="H10" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>18550</v>
+        <v>13400</v>
       </c>
       <c r="K10" t="n">
-        <v>17550</v>
+        <v>13750</v>
       </c>
       <c r="L10" t="n">
-        <v>19580</v>
+        <v>15390</v>
       </c>
       <c r="M10" t="n">
-        <v>17010</v>
+        <v>12380</v>
       </c>
       <c r="N10" t="n">
-        <v>0.88</v>
+        <v>1.01</v>
       </c>
       <c r="O10" t="n">
-        <v>65426657480</v>
+        <v>169096619535</v>
       </c>
       <c r="P10" t="n">
-        <v>30550</v>
+        <v>19380</v>
       </c>
       <c r="Q10" t="n">
-        <v>6100</v>
+        <v>3200</v>
       </c>
       <c r="R10" t="n">
-        <v>-65000</v>
+        <v>-76000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>국내 해킹 초비상 상황 속 보안주 급등 기대감, 아이온큐 주가와의 연관성 언급.</t>
+          <t>호남 반도체 사업 추진 및 중국 반도체 부상 관련 논의. 공매도 세력과의 공방 및 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['해킹', '보안주']</t>
+          <t>['호남 반도체', '공매도', '주가']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17360</v>
+        <v>17330</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.61%</t>
+          <t>'-3.78%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1412,7 +1412,7 @@
         <v>48</v>
       </c>
       <c r="G11" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="H11" t="n">
         <v>27.69</v>
@@ -1438,7 +1438,7 @@
         <v>27.61</v>
       </c>
       <c r="O11" t="n">
-        <v>41677922725</v>
+        <v>42841248280</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15390</v>
+        <v>15420</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.35%</t>
+          <t>'-4.16%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.16</v>
       </c>
       <c r="E12" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="F12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G12" t="n">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="H12" t="n">
         <v>9.630000000000001</v>
@@ -1530,7 +1530,7 @@
         <v>9.470000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>40243372730</v>
+        <v>41130484590</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>전반적인 시장 하락 속에서 대우건설 주가 하락에 대한 우려와 도배 글에 대한 불만.</t>
+          <t>국내 증시 약세 및 건설주 전반의 하락세. 금감원 사모펀드 점검 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['공매도', '시장']</t>
+          <t>['증시', '건설주', '공매도']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6510</v>
+        <v>6470</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.41%</t>
+          <t>'-4.99%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1596,7 +1596,7 @@
         <v>78</v>
       </c>
       <c r="G13" t="n">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="H13" t="n">
         <v>12.27</v>
@@ -1622,7 +1622,7 @@
         <v>12.57</v>
       </c>
       <c r="O13" t="n">
-        <v>17788246410</v>
+        <v>18164721230</v>
       </c>
       <c r="P13" t="n">
         <v>8850</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>68100</v>
+        <v>67800</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.76%</t>
+          <t>'-5.17%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.11</v>
       </c>
       <c r="E14" t="n">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="F14" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G14" t="n">
-        <v>629</v>
+        <v>640</v>
       </c>
       <c r="H14" t="n">
         <v>22.1</v>
@@ -1708,13 +1708,13 @@
         <v>70600</v>
       </c>
       <c r="M14" t="n">
-        <v>68000</v>
+        <v>67600</v>
       </c>
       <c r="N14" t="n">
         <v>22.21</v>
       </c>
       <c r="O14" t="n">
-        <v>100965186050</v>
+        <v>107201660100</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1759,83 +1759,83 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7010</v>
+        <v>7330</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-5.40%</t>
+          <t>'-5.54%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.19</v>
+        <v>-0.36</v>
       </c>
       <c r="E15" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F15" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="G15" t="n">
-        <v>255</v>
+        <v>323</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8</v>
+        <v>26.01</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>7410</v>
+        <v>7760</v>
       </c>
       <c r="K15" t="n">
-        <v>7330</v>
+        <v>7650</v>
       </c>
       <c r="L15" t="n">
-        <v>8040</v>
+        <v>7680</v>
       </c>
       <c r="M15" t="n">
-        <v>6940</v>
+        <v>7300</v>
       </c>
       <c r="N15" t="n">
-        <v>1.99</v>
+        <v>26.37</v>
       </c>
       <c r="O15" t="n">
-        <v>60795787530</v>
+        <v>17425184725</v>
       </c>
       <c r="P15" t="n">
-        <v>23500</v>
+        <v>17950</v>
       </c>
       <c r="Q15" t="n">
-        <v>2890</v>
+        <v>7300</v>
       </c>
       <c r="R15" t="n">
-        <v>-241000</v>
+        <v>-510000</v>
       </c>
       <c r="S15" t="n">
-        <v>-130000</v>
+        <v>19000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>호남 반도체 클러스터 및 신도시 개발 관련 언급. 대차 물량 증가 및 매집 흔적 포착.</t>
+          <t>애플 부품 출하량 감소 및 지속적인 주가 하락세. 회사 경영진 교체 요구 및 적자 관련 비판.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['호남 반도체', '신도시 개발', '매집']</t>
+          <t>['애플', '주가', '적자']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,77 +1844,77 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7335</v>
+        <v>6960</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-5.48%</t>
+          <t>'-6.07%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.36</v>
+        <v>-0.19</v>
       </c>
       <c r="E16" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="F16" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G16" t="n">
-        <v>316</v>
+        <v>260</v>
       </c>
       <c r="H16" t="n">
-        <v>26.01</v>
+        <v>1.8</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>7760</v>
+        <v>7410</v>
       </c>
       <c r="K16" t="n">
-        <v>7650</v>
+        <v>7330</v>
       </c>
       <c r="L16" t="n">
-        <v>7680</v>
+        <v>8040</v>
       </c>
       <c r="M16" t="n">
-        <v>7330</v>
+        <v>6940</v>
       </c>
       <c r="N16" t="n">
-        <v>26.37</v>
+        <v>1.99</v>
       </c>
       <c r="O16" t="n">
-        <v>16447368080</v>
+        <v>61626272545</v>
       </c>
       <c r="P16" t="n">
-        <v>17950</v>
+        <v>23500</v>
       </c>
       <c r="Q16" t="n">
-        <v>7330</v>
+        <v>2890</v>
       </c>
       <c r="R16" t="n">
-        <v>-510000</v>
+        <v>-241000</v>
       </c>
       <c r="S16" t="n">
-        <v>19000</v>
+        <v>-130000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>아이폰 패널 출하량 감소 및 지속적인 주가 하락에 대한 우려, OLED 시장 전망.</t>
+          <t>호남 반도체 클러스터 및 신도시 개발 관련 언급. 대차 물량 증가 및 매집 흔적 포착.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['아이폰', 'OLED']</t>
+          <t>['호남 반도체', '신도시 개발', '매집']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>172500</v>
+        <v>171900</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-7.66%</t>
+          <t>'-7.98%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.02</v>
       </c>
       <c r="E17" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F17" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G17" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H17" t="n">
         <v>75.20999999999999</v>
@@ -1984,13 +1984,13 @@
         <v>183000</v>
       </c>
       <c r="M17" t="n">
-        <v>172500</v>
+        <v>171900</v>
       </c>
       <c r="N17" t="n">
         <v>75.23</v>
       </c>
       <c r="O17" t="n">
-        <v>420087699300</v>
+        <v>436335985950</v>
       </c>
       <c r="P17" t="n">
         <v>243500</v>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>230500</v>
+        <v>229500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-7.98%</t>
+          <t>'-8.38%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2053,10 +2053,10 @@
         <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="G18" t="n">
-        <v>2042</v>
+        <v>2116</v>
       </c>
       <c r="H18" t="n">
         <v>46.3</v>
@@ -2076,13 +2076,13 @@
         <v>244000</v>
       </c>
       <c r="M18" t="n">
-        <v>230000</v>
+        <v>229000</v>
       </c>
       <c r="N18" t="n">
         <v>46.35</v>
       </c>
       <c r="O18" t="n">
-        <v>2736709972000</v>
+        <v>2897894045250</v>
       </c>
       <c r="P18" t="n">
         <v>374500</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>정치적 이슈로 인한 국가 경제 부도 및 주가 하락에 대한 불만 표출.</t>
+          <t>정치권 관련 악재로 인한 증시 전반의 하락세. 정부 정책 및 특정 정치인에 대한 강한 비판.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['정치권', '증시', '정책']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14370</v>
+        <v>14280</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-8.59%</t>
+          <t>'-9.16%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F19" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G19" t="n">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="H19" t="n">
         <v>3.43</v>
@@ -2168,13 +2168,13 @@
         <v>15130</v>
       </c>
       <c r="M19" t="n">
-        <v>14360</v>
+        <v>14270</v>
       </c>
       <c r="N19" t="n">
         <v>3.37</v>
       </c>
       <c r="O19" t="n">
-        <v>60368443675</v>
+        <v>62443835700</v>
       </c>
       <c r="P19" t="n">
         <v>31500</v>
@@ -2190,12 +2190,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>3분기 어닝 서프라이즈 달성 및 외인 대량 매수 확인. 광케이블 기술력 관련 언급.</t>
+          <t>3분기 어닝 서프라이즈 기록 및 외인 대량 매수. 미국 업체 광케이블 기술력 하락으로 인한 반사 이익 기대.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1462000</v>
+        <v>1457000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-8.91%</t>
+          <t>'-9.22%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2237,10 +2237,10 @@
         <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="G20" t="n">
-        <v>2102</v>
+        <v>1934</v>
       </c>
       <c r="H20" t="n">
         <v>49.41</v>
@@ -2266,7 +2266,7 @@
         <v>49.52</v>
       </c>
       <c r="O20" t="n">
-        <v>3632607448500</v>
+        <v>3733491238000</v>
       </c>
       <c r="P20" t="n">
         <v>2987000</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>호남 반도체 이슈 및 정치적 요인으로 인한 외국인 자금 유출 및 주가 하락에 대한 부정적 전망.</t>
+          <t>호남 반도체 사업 추진 및 정치권 이슈로 인한 외국인 자금 유출 우려. 증시 하락에 대한 정치권 책임론 제기.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['호남 반도체', '외국인']</t>
+          <t>['호남 반도체', '외국인', '증시']</t>
         </is>
       </c>
       <c r="X20" t="n">

--- a/data/trending_integrated_20261013_11.xlsx
+++ b/data/trending_integrated_20261013_11.xlsx
@@ -584,7 +584,7 @@
         <v>68</v>
       </c>
       <c r="G2" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H2" t="n">
         <v>1.84</v>
@@ -610,7 +610,7 @@
         <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>87085119490</v>
+        <v>87141083210</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>무차입 경영, 호남 반도체 관련 지역 경제자유구역 확대 수혜 기대감으로 인한 급등 전망.</t>
+          <t>호남 반도체 클러스터 및 지역 개발 수혜 기대감. 연상 랠리 및 대장주로서의 강세 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['경제자유구역', '수혜주']</t>
+          <t>['호남 반도체', '수혜주', '연상']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18715</v>
+        <v>18660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.46%</t>
+          <t>'+14.13%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.25</v>
       </c>
       <c r="E3" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="F3" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G3" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H3" t="n">
         <v>0.88</v>
@@ -702,7 +702,7 @@
         <v>1.13</v>
       </c>
       <c r="O3" t="n">
-        <v>212840574715</v>
+        <v>214453022025</v>
       </c>
       <c r="P3" t="n">
         <v>19930</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>보안 기술 중요성 부각 및 AI 관련 보안 이슈 언급. 신고가 돌파 기대감 속 급등 가능성 언급.</t>
+          <t>보안 기술 중요성 부각 및 관련 뉴스 언급. 기술적 분석 기반 상승 기대감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['보안 기술', 'AI', '신고가']</t>
+          <t>['보안 기술', '해킹', '기술적 분석']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12210</v>
+        <v>12250</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+10.30%</t>
+          <t>'+10.66%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.92</v>
       </c>
       <c r="E4" t="n">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="F4" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="G4" t="n">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="H4" t="n">
         <v>15.64</v>
@@ -794,7 +794,7 @@
         <v>14.72</v>
       </c>
       <c r="O4" t="n">
-        <v>290435601395</v>
+        <v>295230006725</v>
       </c>
       <c r="P4" t="n">
         <v>14350</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>급등 기대감 속 개인 매물 소화 및 물량 확보 중. 호남클러스터 외 테마 소멸. 주포의 매집 정황 포착.</t>
+          <t>호남 클러스터 외 테마 소멸 및 주가 급등 기대감. 투자자 간 매도/보유 논쟁.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['호남클러스터', '주포', '매집']</t>
+          <t>['호남클러스터', '테마', '급등']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1632</v>
+        <v>1640</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.42%</t>
+          <t>'+3.93%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.9399999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F5" t="n">
         <v>21</v>
       </c>
       <c r="G5" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="H5" t="n">
         <v>0.32</v>
@@ -886,7 +886,7 @@
         <v>1.26</v>
       </c>
       <c r="O5" t="n">
-        <v>8211539254</v>
+        <v>8248648868</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13500</v>
+        <v>13400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.67%</t>
+          <t>'-0.07%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.09</v>
       </c>
       <c r="E6" t="n">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="F6" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G6" t="n">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="H6" t="n">
         <v>0.3</v>
@@ -978,7 +978,7 @@
         <v>0.21</v>
       </c>
       <c r="O6" t="n">
-        <v>56491641090</v>
+        <v>57359547325</v>
       </c>
       <c r="P6" t="n">
         <v>28700</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>주가 상승 시 매도세에 눌리는 현상 반복. 공매도 및 대차 상환 관련 언급. 종가 하락에 대한 우려.</t>
+          <t>주가 부양 시도와 매도세 충돌. 공매도 및 대차 관련 언급에도 상승 동력 부족.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['공매도', '매도세', '주가']</t>
+          <t>['공매도', '대차', '매수세']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,70 +1023,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>43300</v>
+        <v>13130</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-2.48%</t>
+          <t>'-2.01%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.23</v>
+        <v>-1.01</v>
       </c>
       <c r="E7" t="n">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="F7" t="n">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="G7" t="n">
-        <v>573</v>
+        <v>277</v>
       </c>
       <c r="H7" t="n">
-        <v>13.1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>44400</v>
+        <v>13400</v>
       </c>
       <c r="K7" t="n">
-        <v>43300</v>
+        <v>13750</v>
       </c>
       <c r="L7" t="n">
-        <v>44100</v>
+        <v>15390</v>
       </c>
       <c r="M7" t="n">
-        <v>42250</v>
+        <v>12380</v>
       </c>
       <c r="N7" t="n">
-        <v>13.33</v>
+        <v>1.01</v>
       </c>
       <c r="O7" t="n">
-        <v>19898568375</v>
+        <v>170861338990</v>
       </c>
       <c r="P7" t="n">
-        <v>69200</v>
+        <v>19380</v>
       </c>
       <c r="Q7" t="n">
-        <v>24150</v>
+        <v>3200</v>
       </c>
       <c r="R7" t="n">
-        <v>45000</v>
+        <v>-76000</v>
       </c>
       <c r="S7" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>간암 1차 치료제 승인 기대감 속 공매도 우려 및 악성 매물대 소화 필요성 언급.</t>
+          <t>데이터센터 건립 및 호남 반도체 투자 관련 언급. 주가 변동성에 대한 엇갈린 평가.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['캄렐리주맙', '공매도', '승인']</t>
+          <t>['데이터센터', '반도체', '변동성']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6010</v>
+        <v>43200</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-3.22%</t>
+          <t>'-2.70%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.06</v>
+        <v>-0.23</v>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>177</v>
       </c>
       <c r="F8" t="n">
-        <v>22</v>
+        <v>102</v>
       </c>
       <c r="G8" t="n">
-        <v>107</v>
+        <v>585</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6899999999999999</v>
+        <v>13.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,60 +1147,60 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>6210</v>
+        <v>44400</v>
       </c>
       <c r="K8" t="n">
-        <v>5950</v>
+        <v>43300</v>
       </c>
       <c r="L8" t="n">
-        <v>6560</v>
+        <v>44100</v>
       </c>
       <c r="M8" t="n">
-        <v>5840</v>
+        <v>42250</v>
       </c>
       <c r="N8" t="n">
-        <v>0.75</v>
+        <v>13.33</v>
       </c>
       <c r="O8" t="n">
-        <v>20816244600</v>
+        <v>20955389975</v>
       </c>
       <c r="P8" t="n">
-        <v>11370</v>
+        <v>69200</v>
       </c>
       <c r="Q8" t="n">
-        <v>3300</v>
+        <v>24150</v>
       </c>
       <c r="R8" t="n">
-        <v>-5000</v>
+        <v>45000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
+          <t>간암 치료제 승인 기대감과 공매도 세력 간의 줄다리기. 재신청 이슈와 IR 데이 일정 주목.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['보안주', '시총', '신용매수']</t>
+          <t>['간암', '승인', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17920</v>
+        <v>17870</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.40%</t>
+          <t>'-3.67%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.42</v>
       </c>
       <c r="E9" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F9" t="n">
         <v>37</v>
       </c>
       <c r="G9" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H9" t="n">
         <v>0.46</v>
@@ -1254,7 +1254,7 @@
         <v>0.88</v>
       </c>
       <c r="O9" t="n">
-        <v>66329191965</v>
+        <v>67582496030</v>
       </c>
       <c r="P9" t="n">
         <v>30550</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>국내 해킹 초비상 상황 속 보안주 급등 기대감, 아이온큐 주가와의 연관성 언급.</t>
+          <t>해킹 관련 이슈에도 지수 및 보안주 흐름에 따라 변동성 예상. 기대감 속 투자자 간 의견 분분.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['해킹', '보안주']</t>
+          <t>['해킹', '보안주', '폭락']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12930</v>
+        <v>17270</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.51%</t>
+          <t>'-4.11%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1.01</v>
+        <v>0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="F10" t="n">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="G10" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>27.69</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,91 +1331,91 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>13400</v>
+        <v>18010</v>
       </c>
       <c r="K10" t="n">
-        <v>13750</v>
+        <v>17430</v>
       </c>
       <c r="L10" t="n">
-        <v>15390</v>
+        <v>17840</v>
       </c>
       <c r="M10" t="n">
-        <v>12380</v>
+        <v>17210</v>
       </c>
       <c r="N10" t="n">
-        <v>1.01</v>
+        <v>27.61</v>
       </c>
       <c r="O10" t="n">
-        <v>169096619535</v>
+        <v>44702308080</v>
       </c>
       <c r="P10" t="n">
-        <v>19380</v>
+        <v>35350</v>
       </c>
       <c r="Q10" t="n">
-        <v>3200</v>
+        <v>17210</v>
       </c>
       <c r="R10" t="n">
-        <v>-76000</v>
+        <v>681000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>71000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>호남 반도체 사업 추진 및 중국 반도체 부상 관련 논의. 공매도 세력과의 공방 및 주가 상승 기대.</t>
+          <t>FLNG 매출 확대 전망 및 목표가 42,000원 제시. 주주 환원 정책 및 공매도 금지 촉구.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['호남 반도체', '공매도', '주가']</t>
+          <t>['FLNG', '매출확대', '주주환원']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17330</v>
+        <v>6480</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.78%</t>
+          <t>'-4.85%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.08</v>
+        <v>-0.3</v>
       </c>
       <c r="E11" t="n">
-        <v>71</v>
+        <v>144</v>
       </c>
       <c r="F11" t="n">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="G11" t="n">
-        <v>253</v>
+        <v>563</v>
       </c>
       <c r="H11" t="n">
-        <v>27.69</v>
+        <v>12.27</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,183 +1423,183 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>18010</v>
+        <v>6810</v>
       </c>
       <c r="K11" t="n">
-        <v>17430</v>
+        <v>7150</v>
       </c>
       <c r="L11" t="n">
-        <v>17840</v>
+        <v>7160</v>
       </c>
       <c r="M11" t="n">
-        <v>17290</v>
+        <v>6440</v>
       </c>
       <c r="N11" t="n">
-        <v>27.61</v>
+        <v>12.57</v>
       </c>
       <c r="O11" t="n">
-        <v>42841248280</v>
+        <v>18362966500</v>
       </c>
       <c r="P11" t="n">
-        <v>35350</v>
+        <v>8850</v>
       </c>
       <c r="Q11" t="n">
-        <v>17290</v>
+        <v>4220</v>
       </c>
       <c r="R11" t="n">
-        <v>681000</v>
+        <v>-606000</v>
       </c>
       <c r="S11" t="n">
-        <v>71000</v>
+        <v>-8000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>FLNG 매출 확대 전망 및 목표가 42,000원 제시. 주주 환원 정책 및 공매도 금지 촉구.</t>
+          <t>의도적인 주가 누르기와 공매도에 대한 불만, 광주 송정역 부지 관련 기대감.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['FLNG', '매출확대', '주주환원']</t>
+          <t>['공매도', '부지']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15420</v>
+        <v>5890</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.16%</t>
+          <t>'-5.15%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.16</v>
+        <v>-0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>115</v>
+        <v>61</v>
       </c>
       <c r="F12" t="n">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="G12" t="n">
-        <v>262</v>
+        <v>114</v>
       </c>
       <c r="H12" t="n">
-        <v>9.630000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>16090</v>
+        <v>6210</v>
       </c>
       <c r="K12" t="n">
-        <v>15190</v>
+        <v>5950</v>
       </c>
       <c r="L12" t="n">
-        <v>15980</v>
+        <v>6560</v>
       </c>
       <c r="M12" t="n">
-        <v>15100</v>
+        <v>5840</v>
       </c>
       <c r="N12" t="n">
-        <v>9.470000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="O12" t="n">
-        <v>41130484590</v>
+        <v>21262356190</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>11370</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>3300</v>
       </c>
       <c r="R12" t="n">
-        <v>395000</v>
+        <v>-5000</v>
       </c>
       <c r="S12" t="n">
-        <v>31000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>국내 증시 약세 및 건설주 전반의 하락세. 금감원 사모펀드 점검 및 공매도 관련 언급.</t>
+          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['증시', '건설주', '공매도']</t>
+          <t>['보안주', '시총', '신용매수']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6470</v>
+        <v>67600</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.99%</t>
+          <t>'-5.45%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.3</v>
+        <v>-0.11</v>
       </c>
       <c r="E13" t="n">
-        <v>141</v>
+        <v>212</v>
       </c>
       <c r="F13" t="n">
-        <v>78</v>
+        <v>143</v>
       </c>
       <c r="G13" t="n">
-        <v>556</v>
+        <v>644</v>
       </c>
       <c r="H13" t="n">
-        <v>12.27</v>
+        <v>22.1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,47 +1607,47 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>6810</v>
+        <v>71500</v>
       </c>
       <c r="K13" t="n">
-        <v>7150</v>
+        <v>68400</v>
       </c>
       <c r="L13" t="n">
-        <v>7160</v>
+        <v>70600</v>
       </c>
       <c r="M13" t="n">
-        <v>6440</v>
+        <v>67300</v>
       </c>
       <c r="N13" t="n">
-        <v>12.57</v>
+        <v>22.21</v>
       </c>
       <c r="O13" t="n">
-        <v>18164721230</v>
+        <v>113319598600</v>
       </c>
       <c r="P13" t="n">
-        <v>8850</v>
+        <v>139200</v>
       </c>
       <c r="Q13" t="n">
-        <v>4220</v>
+        <v>57000</v>
       </c>
       <c r="R13" t="n">
-        <v>-606000</v>
+        <v>225000</v>
       </c>
       <c r="S13" t="n">
-        <v>-8000</v>
+        <v>2000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>의도적인 주가 누르기와 공매도에 대한 불만, 광주 송정역 부지 관련 기대감.</t>
+          <t>정치적 요인 및 시장 상황으로 인한 주가 하락에 대한 불만, 정부 정책 비판.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공매도', '부지']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>67800</v>
+        <v>6980</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-5.17%</t>
+          <t>'-5.80%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.11</v>
+        <v>-0.19</v>
       </c>
       <c r="E14" t="n">
-        <v>197</v>
+        <v>114</v>
       </c>
       <c r="F14" t="n">
-        <v>135</v>
+        <v>48</v>
       </c>
       <c r="G14" t="n">
-        <v>640</v>
+        <v>264</v>
       </c>
       <c r="H14" t="n">
-        <v>22.1</v>
+        <v>1.8</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>71500</v>
+        <v>7410</v>
       </c>
       <c r="K14" t="n">
-        <v>68400</v>
+        <v>7330</v>
       </c>
       <c r="L14" t="n">
-        <v>70600</v>
+        <v>8040</v>
       </c>
       <c r="M14" t="n">
-        <v>67600</v>
+        <v>6890</v>
       </c>
       <c r="N14" t="n">
-        <v>22.21</v>
+        <v>1.99</v>
       </c>
       <c r="O14" t="n">
-        <v>107201660100</v>
+        <v>62231237530</v>
       </c>
       <c r="P14" t="n">
-        <v>139200</v>
+        <v>23500</v>
       </c>
       <c r="Q14" t="n">
-        <v>57000</v>
+        <v>2890</v>
       </c>
       <c r="R14" t="n">
-        <v>225000</v>
+        <v>-241000</v>
       </c>
       <c r="S14" t="n">
-        <v>2000</v>
+        <v>-130000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 요인 및 시장 상황으로 인한 주가 하락에 대한 불만, 정부 정책 비판.</t>
+          <t>성수 메가프로젝트 및 건설기초소재 관련 언급. 매집 물량 확인 및 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['성수메가프로젝트', '건설기초소재', '매집']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7330</v>
+        <v>7310</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-5.54%</t>
+          <t>'-5.80%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.36</v>
       </c>
       <c r="E15" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="F15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G15" t="n">
-        <v>323</v>
+        <v>342</v>
       </c>
       <c r="H15" t="n">
         <v>26.01</v>
@@ -1806,7 +1806,7 @@
         <v>26.37</v>
       </c>
       <c r="O15" t="n">
-        <v>17425184725</v>
+        <v>18349452455</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>애플 부품 출하량 감소 및 지속적인 주가 하락세. 회사 경영진 교체 요구 및 적자 관련 비판.</t>
+          <t>아이폰 부품 축소 및 지속적인 주가 하락 우려. 회사 경영진 사퇴 요구.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['애플', '주가', '적자']</t>
+          <t>['아이폰', '주가 하락', '경영진']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,83 +1851,83 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6960</v>
+        <v>15420</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-6.07%</t>
+          <t>'-7.16%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.19</v>
+        <v>0.16</v>
       </c>
       <c r="E16" t="n">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="F16" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G16" t="n">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>7410</v>
+        <v>16610</v>
       </c>
       <c r="K16" t="n">
-        <v>7330</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>8040</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>6940</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.99</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>61626272545</v>
+        <v>42324000000</v>
       </c>
       <c r="P16" t="n">
-        <v>23500</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2890</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>-241000</v>
+        <v>395000</v>
       </c>
       <c r="S16" t="n">
-        <v>-130000</v>
+        <v>31000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>호남 반도체 클러스터 및 신도시 개발 관련 언급. 대차 물량 증가 및 매집 흔적 포착.</t>
+          <t>주요 건설주 급락 및 시장 불안정성 언급. 대차해지 독려 및 공매도 관련 논의.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['호남 반도체', '신도시 개발', '매집']</t>
+          <t>['건설주', '시장', '공매도']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>171900</v>
+        <v>170900</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-7.98%</t>
+          <t>'-8.51%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.02</v>
       </c>
       <c r="E17" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F17" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G17" t="n">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="H17" t="n">
         <v>75.20999999999999</v>
@@ -1984,13 +1984,13 @@
         <v>183000</v>
       </c>
       <c r="M17" t="n">
-        <v>171900</v>
+        <v>170500</v>
       </c>
       <c r="N17" t="n">
         <v>75.23</v>
       </c>
       <c r="O17" t="n">
-        <v>436335985950</v>
+        <v>458134098150</v>
       </c>
       <c r="P17" t="n">
         <v>243500</v>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>229500</v>
+        <v>229000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-8.38%</t>
+          <t>'-8.58%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2053,10 +2053,10 @@
         <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="G18" t="n">
-        <v>2116</v>
+        <v>1984</v>
       </c>
       <c r="H18" t="n">
         <v>46.3</v>
@@ -2076,13 +2076,13 @@
         <v>244000</v>
       </c>
       <c r="M18" t="n">
-        <v>229000</v>
+        <v>228000</v>
       </c>
       <c r="N18" t="n">
         <v>46.35</v>
       </c>
       <c r="O18" t="n">
-        <v>2897894045250</v>
+        <v>3003476927000</v>
       </c>
       <c r="P18" t="n">
         <v>374500</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>정치권 관련 악재로 인한 증시 전반의 하락세. 정부 정책 및 특정 정치인에 대한 강한 비판.</t>
+          <t>정치권 정책 및 특정 정당 비판, 금융시장 불안정성에 따른 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['정치권', '증시', '정책']</t>
+          <t>['정치', '금융시장', '하락']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14280</v>
+        <v>14290</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-9.16%</t>
+          <t>'-9.10%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F19" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G19" t="n">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H19" t="n">
         <v>3.43</v>
@@ -2168,13 +2168,13 @@
         <v>15130</v>
       </c>
       <c r="M19" t="n">
-        <v>14270</v>
+        <v>14160</v>
       </c>
       <c r="N19" t="n">
         <v>3.37</v>
       </c>
       <c r="O19" t="n">
-        <v>62443835700</v>
+        <v>65376980580</v>
       </c>
       <c r="P19" t="n">
         <v>31500</v>
@@ -2190,12 +2190,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>3분기 어닝 서프라이즈 기록 및 외인 대량 매수. 미국 업체 광케이블 기술력 하락으로 인한 반사 이익 기대.</t>
+          <t>3분기 어닝 서프라이즈 및 외인 대량 매수 확인. 광케이블 기술력 논쟁 및 추세 하락 우려.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1457000</v>
+        <v>1456000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-9.22%</t>
+          <t>'-9.28%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2237,10 +2237,10 @@
         <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="G20" t="n">
-        <v>1934</v>
+        <v>1670</v>
       </c>
       <c r="H20" t="n">
         <v>49.41</v>
@@ -2260,13 +2260,13 @@
         <v>1554000</v>
       </c>
       <c r="M20" t="n">
-        <v>1455000</v>
+        <v>1449000</v>
       </c>
       <c r="N20" t="n">
         <v>49.52</v>
       </c>
       <c r="O20" t="n">
-        <v>3733491238000</v>
+        <v>3914263525500</v>
       </c>
       <c r="P20" t="n">
         <v>2987000</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>호남 반도체 사업 추진 및 정치권 이슈로 인한 외국인 자금 유출 우려. 증시 하락에 대한 정치권 책임론 제기.</t>
+          <t>정치적 이슈와 연계된 주가 하락 및 투자자 손실 우려. 반도체 산업 정책 비판.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['호남 반도체', '외국인', '증시']</t>
+          <t>['정치', '반도체', '하락']</t>
         </is>
       </c>
       <c r="X20" t="n">
